--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G582"/>
+  <dimension ref="A1:G586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16148,6 +16148,114 @@
       <c r="G582" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>406.08</v>
+      </c>
+      <c r="C583" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="D583" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="E583" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="F583" t="n">
+        <v>372.17</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>409.05</v>
+      </c>
+      <c r="C584" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="D584" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="E584" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="F584" t="n">
+        <v>372.17</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>413.15</v>
+      </c>
+      <c r="C585" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="D585" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="E585" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="F585" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>415.87</v>
+      </c>
+      <c r="C586" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="D586" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="E586" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="F586" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22335,6 +22443,46 @@
       </c>
       <c r="B617" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -22503,28 +22651,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7077631662067581</v>
+        <v>-0.7148056375519717</v>
       </c>
       <c r="J2" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K2" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0276583366732136</v>
+        <v>0.02858721463456226</v>
       </c>
       <c r="M2" t="n">
-        <v>27.18098107894847</v>
+        <v>27.02819897064887</v>
       </c>
       <c r="N2" t="n">
-        <v>992.1822708260482</v>
+        <v>985.6766616713925</v>
       </c>
       <c r="O2" t="n">
-        <v>31.49892491540066</v>
+        <v>31.39548791898913</v>
       </c>
       <c r="P2" t="n">
-        <v>435.0357249283328</v>
+        <v>435.1076772649099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22581,28 +22729,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1379527068438804</v>
+        <v>-0.1395821981675955</v>
       </c>
       <c r="J3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1360754726525349</v>
+        <v>0.1404034857454453</v>
       </c>
       <c r="M3" t="n">
-        <v>2.036215340750315</v>
+        <v>2.030140204110837</v>
       </c>
       <c r="N3" t="n">
-        <v>6.844655691922781</v>
+        <v>6.808733453018794</v>
       </c>
       <c r="O3" t="n">
-        <v>2.616229288866475</v>
+        <v>2.609354987926862</v>
       </c>
       <c r="P3" t="n">
-        <v>380.1887644675604</v>
+        <v>380.2053514296776</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22659,28 +22807,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05197169256655436</v>
+        <v>0.04615337558891852</v>
       </c>
       <c r="J4" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K4" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02562234224590387</v>
+        <v>0.02015198631597848</v>
       </c>
       <c r="M4" t="n">
-        <v>1.890851130847343</v>
+        <v>1.911351727363388</v>
       </c>
       <c r="N4" t="n">
-        <v>5.818853349303133</v>
+        <v>5.912039236043626</v>
       </c>
       <c r="O4" t="n">
-        <v>2.412229953653493</v>
+        <v>2.431468534866044</v>
       </c>
       <c r="P4" t="n">
-        <v>375.5241732497605</v>
+        <v>375.5833929417453</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22737,28 +22885,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005227731293546494</v>
+        <v>-0.003296518883837887</v>
       </c>
       <c r="J5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L5" t="n">
-        <v>2.123171507828481e-06</v>
+        <v>8.496555645287618e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.095382388189174</v>
+        <v>2.098413991133682</v>
       </c>
       <c r="N5" t="n">
-        <v>7.291816229553492</v>
+        <v>7.299966018452838</v>
       </c>
       <c r="O5" t="n">
-        <v>2.700336317859961</v>
+        <v>2.701844928646505</v>
       </c>
       <c r="P5" t="n">
-        <v>375.2726131180185</v>
+        <v>375.3114894967819</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22815,28 +22963,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0622504289793552</v>
+        <v>-0.0664414964130299</v>
       </c>
       <c r="J6" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K6" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02847668430631844</v>
+        <v>0.0324661214378511</v>
       </c>
       <c r="M6" t="n">
-        <v>2.120186340898139</v>
+        <v>2.129270056001372</v>
       </c>
       <c r="N6" t="n">
-        <v>7.501343055094229</v>
+        <v>7.521268086221913</v>
       </c>
       <c r="O6" t="n">
-        <v>2.738857983739615</v>
+        <v>2.742493042146491</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4372881140776</v>
+        <v>376.4799231640283</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22874,7 +23022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G582"/>
+  <dimension ref="A1:G586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44403,6 +44551,154 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-35.01453720618017,173.85919945899366</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>-35.01517899284949,173.85866023784115</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-35.01588850637168,173.8585202924401</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>-35.01660062947964,173.85864534818873</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>-35.01731348251367,173.85884360703398</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-35.0145434170063,173.8592311221221</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>-35.01517958661369,173.85866433959185</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-35.01588850637168,173.8585202924401</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-35.01660062947964,173.85864534818873</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>-35.01731348251367,173.85884360703398</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-35.01455199086033,173.85927483217236</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-35.0151785865897,173.85865743138018</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-35.015888465993484,173.8585237992952</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-35.01660179933876,173.8586379206209</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-35.01731592501428,173.85883124473625</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-35.0145576788718,173.85930383006422</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-35.0151785865897,173.85865743138018</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-35.015888465993484,173.8585237992952</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-35.01660179933876,173.8586379206209</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-35.01731592501428,173.85883124473625</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G586"/>
+  <dimension ref="A1:G588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16251,9 +16251,63 @@
         <v>372.02</v>
       </c>
       <c r="F586" t="n">
-        <v>371.01</v>
+        <v>373.42</v>
       </c>
       <c r="G586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>430.46</v>
+      </c>
+      <c r="C587" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="D587" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="E587" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="F587" t="n">
+        <v>372.61</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>431.33</v>
+      </c>
+      <c r="C588" t="n">
+        <v>372.43</v>
+      </c>
+      <c r="D588" t="n">
+        <v>372.32</v>
+      </c>
+      <c r="E588" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="F588" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="G588" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16270,7 +16324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22483,6 +22537,26 @@
       </c>
       <c r="B621" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -22651,28 +22725,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7148056375519717</v>
+        <v>-0.7052089453755988</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K2" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02858721463456226</v>
+        <v>0.02802157182198473</v>
       </c>
       <c r="M2" t="n">
-        <v>27.02819897064887</v>
+        <v>26.99007741104079</v>
       </c>
       <c r="N2" t="n">
-        <v>985.6766616713925</v>
+        <v>983.0389764580207</v>
       </c>
       <c r="O2" t="n">
-        <v>31.39548791898913</v>
+        <v>31.35345238499296</v>
       </c>
       <c r="P2" t="n">
-        <v>435.1076772649099</v>
+        <v>435.0091864571024</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22729,28 +22803,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1395821981675955</v>
+        <v>-0.1421543747465271</v>
       </c>
       <c r="J3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1404034857454453</v>
+        <v>0.1448030821279164</v>
       </c>
       <c r="M3" t="n">
-        <v>2.030140204110837</v>
+        <v>2.035564028325926</v>
       </c>
       <c r="N3" t="n">
-        <v>6.808733453018794</v>
+        <v>6.838139491623575</v>
       </c>
       <c r="O3" t="n">
-        <v>2.609354987926862</v>
+        <v>2.614983650354926</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2053514296776</v>
+        <v>380.2316413355725</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22807,28 +22881,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04615337558891852</v>
+        <v>0.04323736060293603</v>
       </c>
       <c r="J4" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K4" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02015198631597848</v>
+        <v>0.01765656697633167</v>
       </c>
       <c r="M4" t="n">
-        <v>1.911351727363388</v>
+        <v>1.921924454643671</v>
       </c>
       <c r="N4" t="n">
-        <v>5.912039236043626</v>
+        <v>5.959428388996227</v>
       </c>
       <c r="O4" t="n">
-        <v>2.431468534866044</v>
+        <v>2.441194049844507</v>
       </c>
       <c r="P4" t="n">
-        <v>375.5833929417453</v>
+        <v>375.6131966642756</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22885,28 +22959,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.003296518883837887</v>
+        <v>-0.006080032191381901</v>
       </c>
       <c r="J5" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K5" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L5" t="n">
-        <v>8.496555645287618e-05</v>
+        <v>0.0002886124812072621</v>
       </c>
       <c r="M5" t="n">
-        <v>2.098413991133682</v>
+        <v>2.103982777239134</v>
       </c>
       <c r="N5" t="n">
-        <v>7.299966018452838</v>
+        <v>7.336694977833848</v>
       </c>
       <c r="O5" t="n">
-        <v>2.701844928646505</v>
+        <v>2.708633415180771</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3114894967819</v>
+        <v>375.3399394401761</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22963,28 +23037,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0664414964130299</v>
+        <v>-0.06707007522388003</v>
       </c>
       <c r="J6" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K6" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0324661214378511</v>
+        <v>0.03331379812320634</v>
       </c>
       <c r="M6" t="n">
-        <v>2.129270056001372</v>
+        <v>2.125484889611168</v>
       </c>
       <c r="N6" t="n">
-        <v>7.521268086221913</v>
+        <v>7.490847375093495</v>
       </c>
       <c r="O6" t="n">
-        <v>2.742493042146491</v>
+        <v>2.736941244362673</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4799231640283</v>
+        <v>376.4863726297032</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23022,7 +23096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G586"/>
+  <dimension ref="A1:G588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44690,10 +44764,84 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>-35.01731592501428,173.85883124473625</t>
+          <t>-35.0173108505073,173.85885692847467</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-35.01458818907867,173.8594593739695</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-35.01517486774697,173.8586317414695</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-35.0158885000626,173.8585208403862</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-35.016603359150224,173.85862801719674</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-35.017312556047585,173.8588482961812</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-35.014590008392396,173.85946864903795</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-35.01517443023571,173.8586287191272</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-35.01588850132442,173.85852073079698</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-35.01660385082975,173.85862489546514</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-35.01731274555202,173.85884733703747</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G588"/>
+  <dimension ref="A1:G590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16310,6 +16310,60 @@
       <c r="G588" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>440.04</v>
+      </c>
+      <c r="C589" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="D589" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="E589" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="F589" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>454.69</v>
+      </c>
+      <c r="C590" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="D590" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="E590" t="n">
+        <v>371.51</v>
+      </c>
+      <c r="F590" t="n">
+        <v>374.24</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16324,7 +16378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B623"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22557,6 +22611,26 @@
       </c>
       <c r="B623" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -22725,28 +22799,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7052089453755988</v>
+        <v>-0.6849864385033424</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K2" t="n">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02802157182198473</v>
+        <v>0.02657502138961221</v>
       </c>
       <c r="M2" t="n">
-        <v>26.99007741104079</v>
+        <v>27.01175103364368</v>
       </c>
       <c r="N2" t="n">
-        <v>983.0389764580207</v>
+        <v>983.1173790094837</v>
       </c>
       <c r="O2" t="n">
-        <v>31.35345238499296</v>
+        <v>31.35470266179355</v>
       </c>
       <c r="P2" t="n">
-        <v>435.0091864571024</v>
+        <v>434.8009672701123</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22803,28 +22877,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1421543747465271</v>
+        <v>-0.1450606015645609</v>
       </c>
       <c r="J3" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K3" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1448030821279164</v>
+        <v>0.1495274566918018</v>
       </c>
       <c r="M3" t="n">
-        <v>2.035564028325926</v>
+        <v>2.042641947116886</v>
       </c>
       <c r="N3" t="n">
-        <v>6.838139491623575</v>
+        <v>6.883420685677152</v>
       </c>
       <c r="O3" t="n">
-        <v>2.614983650354926</v>
+        <v>2.623627390784971</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2316413355725</v>
+        <v>380.2614264889103</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22881,28 +22955,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04323736060293603</v>
+        <v>0.03999939335537257</v>
       </c>
       <c r="J4" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K4" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01765656697633167</v>
+        <v>0.01504690280649079</v>
       </c>
       <c r="M4" t="n">
-        <v>1.921924454643671</v>
+        <v>1.934337186930738</v>
       </c>
       <c r="N4" t="n">
-        <v>5.959428388996227</v>
+        <v>6.023393796106138</v>
       </c>
       <c r="O4" t="n">
-        <v>2.441194049844507</v>
+        <v>2.454260335845841</v>
       </c>
       <c r="P4" t="n">
-        <v>375.6131966642756</v>
+        <v>375.6463843538069</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22959,28 +23033,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.006080032191381901</v>
+        <v>-0.008964211292664054</v>
       </c>
       <c r="J5" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K5" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002886124812072621</v>
+        <v>0.0006258030203325493</v>
       </c>
       <c r="M5" t="n">
-        <v>2.103982777239134</v>
+        <v>2.110132164249898</v>
       </c>
       <c r="N5" t="n">
-        <v>7.336694977833848</v>
+        <v>7.380412910283428</v>
       </c>
       <c r="O5" t="n">
-        <v>2.708633415180771</v>
+        <v>2.716691537566131</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3399394401761</v>
+        <v>375.3694960172882</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23037,28 +23111,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06707007522388003</v>
+        <v>-0.06819782691454547</v>
       </c>
       <c r="J6" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K6" t="n">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03331379812320634</v>
+        <v>0.0345730618468244</v>
       </c>
       <c r="M6" t="n">
-        <v>2.125484889611168</v>
+        <v>2.124512540286616</v>
       </c>
       <c r="N6" t="n">
-        <v>7.490847375093495</v>
+        <v>7.48113204058338</v>
       </c>
       <c r="O6" t="n">
-        <v>2.736941244362673</v>
+        <v>2.735165815921108</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4863726297032</v>
+        <v>376.4979126763528</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23096,7 +23170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G588"/>
+  <dimension ref="A1:G590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44847,6 +44921,80 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-35.01460822240186,173.85956150635448</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-35.01517291457108,173.85861824887024</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-35.015888613625805,173.85851097735613</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-35.01660530891342,173.85861563791602</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-35.01731449320374,173.85883849160052</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-35.014638857744,173.85971769010513</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-35.015174555238936,173.85862958265358</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-35.01588852908438,173.85851831983408</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-35.01660266401696,173.8586324306793</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-35.017309123910316,173.85886566733927</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G590"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16364,6 +16364,60 @@
       <c r="G590" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>461.18</v>
+      </c>
+      <c r="C591" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D591" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="E591" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="F591" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>460.67</v>
+      </c>
+      <c r="C592" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="D592" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="E592" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="F592" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22631,6 +22685,26 @@
       </c>
       <c r="B625" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -22799,28 +22873,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6849864385033424</v>
+        <v>-0.6562547318590206</v>
       </c>
       <c r="J2" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K2" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02657502138961221</v>
+        <v>0.02445714370053031</v>
       </c>
       <c r="M2" t="n">
-        <v>27.01175103364368</v>
+        <v>27.08141159421625</v>
       </c>
       <c r="N2" t="n">
-        <v>983.1173790094837</v>
+        <v>986.3683428803884</v>
       </c>
       <c r="O2" t="n">
-        <v>31.35470266179355</v>
+        <v>31.40650160206304</v>
       </c>
       <c r="P2" t="n">
-        <v>434.8009672701123</v>
+        <v>434.504328353972</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22877,28 +22951,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1450606015645609</v>
+        <v>-0.1472419284958701</v>
       </c>
       <c r="J3" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K3" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1495274566918018</v>
+        <v>0.1535684192595554</v>
       </c>
       <c r="M3" t="n">
-        <v>2.042641947116886</v>
+        <v>2.046179946590383</v>
       </c>
       <c r="N3" t="n">
-        <v>6.883420685677152</v>
+        <v>6.898509187159498</v>
       </c>
       <c r="O3" t="n">
-        <v>2.623627390784971</v>
+        <v>2.626501320608748</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2614264889103</v>
+        <v>380.2838549549485</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22955,28 +23029,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03999939335537257</v>
+        <v>0.03734801964613571</v>
       </c>
       <c r="J4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01504690280649079</v>
+        <v>0.01311468698645923</v>
       </c>
       <c r="M4" t="n">
-        <v>1.934337186930738</v>
+        <v>1.943152293055953</v>
       </c>
       <c r="N4" t="n">
-        <v>6.023393796106138</v>
+        <v>6.059631599573152</v>
       </c>
       <c r="O4" t="n">
-        <v>2.454260335845841</v>
+        <v>2.461631897659184</v>
       </c>
       <c r="P4" t="n">
-        <v>375.6463843538069</v>
+        <v>375.6736460707193</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23033,28 +23107,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008964211292664054</v>
+        <v>-0.0108173866192519</v>
       </c>
       <c r="J5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006258030203325493</v>
+        <v>0.0009141350169266094</v>
       </c>
       <c r="M5" t="n">
-        <v>2.110132164249898</v>
+        <v>2.111556693439963</v>
       </c>
       <c r="N5" t="n">
-        <v>7.380412910283428</v>
+        <v>7.383112420568667</v>
       </c>
       <c r="O5" t="n">
-        <v>2.716691537566131</v>
+        <v>2.717188329978006</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3694960172882</v>
+        <v>375.3885516420801</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23111,28 +23185,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06819782691454547</v>
+        <v>-0.06775039506933614</v>
       </c>
       <c r="J6" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K6" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0345730618468244</v>
+        <v>0.03436574694582206</v>
       </c>
       <c r="M6" t="n">
-        <v>2.124512540286616</v>
+        <v>2.119507446321326</v>
       </c>
       <c r="N6" t="n">
-        <v>7.48113204058338</v>
+        <v>7.457398797163878</v>
       </c>
       <c r="O6" t="n">
-        <v>2.735165815921108</v>
+        <v>2.730823831220879</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4979126763528</v>
+        <v>376.4933150350773</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23170,7 +23244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G590"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44995,6 +45069,80 @@
         </is>
       </c>
     </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-35.01465242924029,173.85978688007566</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-35.01517505525178,173.85863303675904</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-35.01588848996804,173.85852171709996</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-35.0166011381141,173.85864211881145</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-35.01730657612585,173.85887856249244</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-35.01465136276052,173.8597814429585</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-35.015175680267696,173.85863735439096</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-35.01588844201888,173.85852588149044</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-35.01660164674846,173.8586388894341</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-35.01730684985483,173.85887717706282</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16418,6 +16418,114 @@
       <c r="G592" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>459.86</v>
+      </c>
+      <c r="C593" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="D593" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="E593" t="n">
+        <v>371.32</v>
+      </c>
+      <c r="F593" t="n">
+        <v>374.94</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="C594" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="D594" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="E594" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="F594" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>454.29</v>
+      </c>
+      <c r="C595" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="D595" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="E595" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="F595" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>449.25</v>
+      </c>
+      <c r="C596" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="D596" t="n">
+        <v>372.27</v>
+      </c>
+      <c r="E596" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="F596" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16432,7 +16540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22705,6 +22813,46 @@
       </c>
       <c r="B627" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22873,28 +23021,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6562547318590206</v>
+        <v>-0.6068803874516856</v>
       </c>
       <c r="J2" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K2" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02445714370053031</v>
+        <v>0.02107853789935676</v>
       </c>
       <c r="M2" t="n">
-        <v>27.08141159421625</v>
+        <v>27.17176273928664</v>
       </c>
       <c r="N2" t="n">
-        <v>986.3683428803884</v>
+        <v>989.6073185603827</v>
       </c>
       <c r="O2" t="n">
-        <v>31.40650160206304</v>
+        <v>31.4580247084966</v>
       </c>
       <c r="P2" t="n">
-        <v>434.504328353972</v>
+        <v>433.9919567495412</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22951,28 +23099,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1472419284958701</v>
+        <v>-0.1526901081636159</v>
       </c>
       <c r="J3" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K3" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1535684192595554</v>
+        <v>0.1628153256788917</v>
       </c>
       <c r="M3" t="n">
-        <v>2.046179946590383</v>
+        <v>2.058503067621158</v>
       </c>
       <c r="N3" t="n">
-        <v>6.898509187159498</v>
+        <v>6.973265757911289</v>
       </c>
       <c r="O3" t="n">
-        <v>2.626501320608748</v>
+        <v>2.64069418106514</v>
       </c>
       <c r="P3" t="n">
-        <v>380.2838549549485</v>
+        <v>380.3401704831742</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23029,28 +23177,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03734801964613571</v>
+        <v>0.03222841699446892</v>
       </c>
       <c r="J4" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K4" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01311468698645923</v>
+        <v>0.00976729257946396</v>
       </c>
       <c r="M4" t="n">
-        <v>1.943152293055953</v>
+        <v>1.959392098838491</v>
       </c>
       <c r="N4" t="n">
-        <v>6.059631599573152</v>
+        <v>6.125329313554207</v>
       </c>
       <c r="O4" t="n">
-        <v>2.461631897659184</v>
+        <v>2.474940264643615</v>
       </c>
       <c r="P4" t="n">
-        <v>375.6736460707193</v>
+        <v>375.726568237219</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23107,28 +23255,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0108173866192519</v>
+        <v>-0.01655220129038082</v>
       </c>
       <c r="J5" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K5" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009141350169266094</v>
+        <v>0.002129522221645419</v>
       </c>
       <c r="M5" t="n">
-        <v>2.111556693439963</v>
+        <v>2.123611887874809</v>
       </c>
       <c r="N5" t="n">
-        <v>7.383112420568667</v>
+        <v>7.467787309353263</v>
       </c>
       <c r="O5" t="n">
-        <v>2.717188329978006</v>
+        <v>2.732725253177359</v>
       </c>
       <c r="P5" t="n">
-        <v>375.3885516420801</v>
+        <v>375.4478323513595</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23185,28 +23333,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06775039506933614</v>
+        <v>-0.06833385055628659</v>
       </c>
       <c r="J6" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K6" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03436574694582206</v>
+        <v>0.03541342486996002</v>
       </c>
       <c r="M6" t="n">
-        <v>2.119507446321326</v>
+        <v>2.109297177092581</v>
       </c>
       <c r="N6" t="n">
-        <v>7.457398797163878</v>
+        <v>7.40968511691869</v>
       </c>
       <c r="O6" t="n">
-        <v>2.730823831220879</v>
+        <v>2.72207367955364</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4933150350773</v>
+        <v>376.4993481158229</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23244,7 +23392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45143,6 +45291,154 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-35.01464966893918,173.85977280753747</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-35.01517464899135,173.85863023029833</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-35.01588839406955,173.85853004588088</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-35.0166029861519,173.85863038540688</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-35.01730764998559,173.85887312734533</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-35.01464703410478,173.859759374661</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-35.0151730551998,173.85861922033737</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-35.01588846346984,173.85852401847367</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-35.01660520718667,173.85861628379155</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-35.017309523975534,173.85886364248043</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-35.01463802128684,173.85971342570087</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-35.01517335208261,173.85862127121243</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-35.0158884672553,173.858523689706</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-35.01660466464399,173.85861972846104</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-35.017309523975534,173.85886364248043</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-35.01462748191367,173.85965969421463</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-35.01517457086434,173.85862969059437</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-35.015888507633505,173.85852018285087</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-35.01660390169315,173.8586245725274</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>-35.017309860872516,173.85886193733614</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G596"/>
+  <dimension ref="A1:G599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16524,6 +16524,87 @@
         <v>373.89</v>
       </c>
       <c r="G596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>445.56</v>
+      </c>
+      <c r="C597" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="D597" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="E597" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="F597" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>439.76</v>
+      </c>
+      <c r="C598" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="D598" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="E598" t="n">
+        <v>370.02</v>
+      </c>
+      <c r="F598" t="n">
+        <v>373.99</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>433.83</v>
+      </c>
+      <c r="C599" t="n">
+        <v>372.72</v>
+      </c>
+      <c r="D599" t="n">
+        <v>373.38</v>
+      </c>
+      <c r="E599" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="F599" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="G599" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16540,7 +16621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B631"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22853,6 +22934,36 @@
       </c>
       <c r="B631" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -23021,28 +23132,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6068803874516856</v>
+        <v>-0.585964050388285</v>
       </c>
       <c r="J2" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K2" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02107853789935676</v>
+        <v>0.01983572597699423</v>
       </c>
       <c r="M2" t="n">
-        <v>27.17176273928664</v>
+        <v>27.15047186032723</v>
       </c>
       <c r="N2" t="n">
-        <v>989.6073185603827</v>
+        <v>987.1307689543748</v>
       </c>
       <c r="O2" t="n">
-        <v>31.4580247084966</v>
+        <v>31.41863728671845</v>
       </c>
       <c r="P2" t="n">
-        <v>433.9919567495412</v>
+        <v>433.7742065718678</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23099,28 +23210,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1526901081636159</v>
+        <v>-0.1562533379790308</v>
       </c>
       <c r="J3" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K3" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1628153256788917</v>
+        <v>0.1692877248297047</v>
       </c>
       <c r="M3" t="n">
-        <v>2.058503067621158</v>
+        <v>2.065663110387511</v>
       </c>
       <c r="N3" t="n">
-        <v>6.973265757911289</v>
+        <v>7.008059867589599</v>
       </c>
       <c r="O3" t="n">
-        <v>2.64069418106514</v>
+        <v>2.647274044671159</v>
       </c>
       <c r="P3" t="n">
-        <v>380.3401704831742</v>
+        <v>380.3771212552091</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23177,28 +23288,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03222841699446892</v>
+        <v>0.0285716376993808</v>
       </c>
       <c r="J4" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K4" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00976729257946396</v>
+        <v>0.007681095849590092</v>
       </c>
       <c r="M4" t="n">
-        <v>1.959392098838491</v>
+        <v>1.970640999337745</v>
       </c>
       <c r="N4" t="n">
-        <v>6.125329313554207</v>
+        <v>6.168966122356276</v>
       </c>
       <c r="O4" t="n">
-        <v>2.474940264643615</v>
+        <v>2.483740349222574</v>
       </c>
       <c r="P4" t="n">
-        <v>375.726568237219</v>
+        <v>375.7644873216219</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23255,28 +23366,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01655220129038082</v>
+        <v>-0.02127249963101156</v>
       </c>
       <c r="J5" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K5" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002129522221645419</v>
+        <v>0.003491873969616255</v>
       </c>
       <c r="M5" t="n">
-        <v>2.123611887874809</v>
+        <v>2.134327694159457</v>
       </c>
       <c r="N5" t="n">
-        <v>7.467787309353263</v>
+        <v>7.553937191920204</v>
       </c>
       <c r="O5" t="n">
-        <v>2.732725253177359</v>
+        <v>2.748442684852679</v>
       </c>
       <c r="P5" t="n">
-        <v>375.4478323513595</v>
+        <v>375.4967887843274</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23333,28 +23444,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06833385055628659</v>
+        <v>-0.06896442668297946</v>
       </c>
       <c r="J6" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="K6" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03541342486996002</v>
+        <v>0.03640574700849442</v>
       </c>
       <c r="M6" t="n">
-        <v>2.109297177092581</v>
+        <v>2.102169356736601</v>
       </c>
       <c r="N6" t="n">
-        <v>7.40968511691869</v>
+        <v>7.374772749488445</v>
       </c>
       <c r="O6" t="n">
-        <v>2.72207367955364</v>
+        <v>2.715653282267168</v>
       </c>
       <c r="P6" t="n">
-        <v>376.4993481158229</v>
+        <v>376.5058822785201</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23392,7 +23503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G596"/>
+  <dimension ref="A1:G599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45439,6 +45550,117 @@
         </is>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-35.01461976557166,173.8596203550992</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-35.01517419585464,173.85862710001527</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-35.01588849249168,173.85852149792154</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-35.01660400341994,173.8586239266519</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-35.01731000826495,173.8588611913355</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-35.01460763687799,173.85955852127367</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-35.015174555238936,173.85862958265358</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-35.015888486182604,173.85852204586766</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-35.016605190232205,173.85861639143747</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-35.0173096503119,173.85886300305134</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-35.01459523630142,173.85949530153576</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-35.01517488337237,173.8586318494103</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-35.015888367571165,173.85853234725457</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-35.01660629227177,173.85860939445246</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-35.01730916602246,173.85886545419623</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0049/nzd0049.xlsx
+++ b/data/nzd0049/nzd0049.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G599"/>
+  <dimension ref="A1:G604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16605,6 +16605,141 @@
         <v>374.22</v>
       </c>
       <c r="G599" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>428.19</v>
+      </c>
+      <c r="C600" t="n">
+        <v>371.91</v>
+      </c>
+      <c r="D600" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="E600" t="n">
+        <v>368.19</v>
+      </c>
+      <c r="F600" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>418.79</v>
+      </c>
+      <c r="C601" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="D601" t="n">
+        <v>373</v>
+      </c>
+      <c r="E601" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="F601" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>416.47</v>
+      </c>
+      <c r="C602" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="D602" t="n">
+        <v>373.29</v>
+      </c>
+      <c r="E602" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="F602" t="n">
+        <v>375.18</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>411.14</v>
+      </c>
+      <c r="C603" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="D603" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="E603" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="F603" t="n">
+        <v>372.14</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>408.02</v>
+      </c>
+      <c r="C604" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="D604" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="E604" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="F604" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="G604" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16621,7 +16756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B634"/>
+  <dimension ref="A1:B639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22964,6 +23099,56 @@
       </c>
       <c r="B634" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -23132,28 +23317,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.585964050388285</v>
+        <v>-0.5883811063951375</v>
       </c>
       <c r="J2" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K2" t="n">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01983572597699423</v>
+        <v>0.02033447985492354</v>
       </c>
       <c r="M2" t="n">
-        <v>27.15047186032723</v>
+        <v>26.97311479467404</v>
       </c>
       <c r="N2" t="n">
-        <v>987.1307689543748</v>
+        <v>979.353098544032</v>
       </c>
       <c r="O2" t="n">
-        <v>31.41863728671845</v>
+        <v>31.29461772484259</v>
       </c>
       <c r="P2" t="n">
-        <v>433.7742065718678</v>
+        <v>433.7995620369558</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23210,28 +23395,28 @@
         <v>0.0673</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1562533379790308</v>
+        <v>-0.1633022544390652</v>
       </c>
       <c r="J3" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K3" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1692877248297047</v>
+        <v>0.1810956787515151</v>
       </c>
       <c r="M3" t="n">
-        <v>2.065663110387511</v>
+        <v>2.083447165964731</v>
       </c>
       <c r="N3" t="n">
-        <v>7.008059867589599</v>
+        <v>7.118805193377342</v>
       </c>
       <c r="O3" t="n">
-        <v>2.647274044671159</v>
+        <v>2.668108917075414</v>
       </c>
       <c r="P3" t="n">
-        <v>380.3771212552091</v>
+        <v>380.4505258746232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23288,28 +23473,28 @@
         <v>0.1342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0285716376993808</v>
+        <v>0.02209241731299021</v>
       </c>
       <c r="J4" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K4" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007681095849590092</v>
+        <v>0.004580192847706055</v>
       </c>
       <c r="M4" t="n">
-        <v>1.970640999337745</v>
+        <v>1.992796749402351</v>
       </c>
       <c r="N4" t="n">
-        <v>6.168966122356276</v>
+        <v>6.261907714714127</v>
       </c>
       <c r="O4" t="n">
-        <v>2.483740349222574</v>
+        <v>2.502380409672783</v>
       </c>
       <c r="P4" t="n">
-        <v>375.7644873216219</v>
+        <v>375.8319635292821</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23366,28 +23551,28 @@
         <v>0.0914</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02127249963101156</v>
+        <v>-0.03086806561946719</v>
       </c>
       <c r="J5" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K5" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003491873969616255</v>
+        <v>0.00715868935709385</v>
       </c>
       <c r="M5" t="n">
-        <v>2.134327694159457</v>
+        <v>2.160519779115921</v>
       </c>
       <c r="N5" t="n">
-        <v>7.553937191920204</v>
+        <v>7.801225365624827</v>
       </c>
       <c r="O5" t="n">
-        <v>2.748442684852679</v>
+        <v>2.793067375776107</v>
       </c>
       <c r="P5" t="n">
-        <v>375.4967887843274</v>
+        <v>375.5967156042024</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23444,28 +23629,28 @@
         <v>0.0531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06896442668297946</v>
+        <v>-0.0705998352158267</v>
       </c>
       <c r="J6" t="n">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="K6" t="n">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03640574700849442</v>
+        <v>0.03864011277014368</v>
       </c>
       <c r="M6" t="n">
-        <v>2.102169356736601</v>
+        <v>2.095455195476893</v>
       </c>
       <c r="N6" t="n">
-        <v>7.374772749488445</v>
+        <v>7.331663646912737</v>
       </c>
       <c r="O6" t="n">
-        <v>2.715653282267168</v>
+        <v>2.70770449770885</v>
       </c>
       <c r="P6" t="n">
-        <v>376.5058822785201</v>
+        <v>376.5229095973844</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23503,7 +23688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G599"/>
+  <dimension ref="A1:G604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45661,6 +45846,191 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-35.014583442130295,173.85943517350535</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-35.015173617714574,173.8586231062059</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-35.015888555582485,173.8585160184604</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-35.01660829289639,173.85859669223302</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-35.0173108505073,173.85885692847467</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-35.01456378511163,173.85933496015835</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-35.01517169578856,173.8586098294886</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-35.01588841552058,173.85852818286412</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-35.01660729258425,173.8586030433428</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-35.01730897651787,173.85886641333988</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-35.01455893357928,173.85931022665855</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-35.0151729301965,173.85861835681104</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-35.01588837892762,173.8585313609516</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-35.016605851456006,173.8586121932465</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-35.01730714463985,173.85887568506163</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-35.014547787582664,173.85925340358565</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-35.015173445835075,173.85862191885718</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-35.0158885997459,173.8585121828376</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-35.01660791989868,173.85859906044348</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>-35.01731354568181,173.85884328731942</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-35.014541263084375,173.859220141306</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-35.015174367734105,173.858628287364</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-35.015888530346196,173.85851821024485</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-35.01660732649314,173.85860282805098</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>-35.017311776973706,173.85885223932763</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
